--- a/fixtures/sml/cell/formula/concat.xlsx
+++ b/fixtures/sml/cell/formula/concat.xlsx
@@ -10,10 +10,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>World</t>
+    <t>Hello</t>
   </si>
   <si>
-    <t>Hello</t>
+    <t>World</t>
   </si>
 </sst>
 </file>
@@ -23,10 +23,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1">
         <f>A1&amp;" "&amp;B1</f>
